--- a/data/trans_bre/P34A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 5,79</t>
+          <t>-10,54; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 18,92</t>
+          <t>3,84; 19,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 17,91</t>
+          <t>1,14; 16,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 16,57</t>
+          <t>0,09; 16,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 17,7</t>
+          <t>-26,3; 18,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 91,55</t>
+          <t>13,1; 95,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 63,46</t>
+          <t>3,29; 60,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 45,06</t>
+          <t>0,09; 44,44</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 16,51</t>
+          <t>4,25; 16,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 19,39</t>
+          <t>8,15; 19,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 13,07</t>
+          <t>1,94; 13,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 21,03</t>
+          <t>8,31; 21,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,63; 55,78</t>
+          <t>11,93; 55,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,45; 97,82</t>
+          <t>32,79; 104,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 50,24</t>
+          <t>5,54; 50,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,19; 63,07</t>
+          <t>19,7; 65,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 6,49</t>
+          <t>-8,82; 6,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 6,73</t>
+          <t>-5,9; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 12,37</t>
+          <t>-2,33; 11,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 9,93</t>
+          <t>-4,05; 9,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 17,52</t>
+          <t>-19,73; 16,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 43,04</t>
+          <t>-26,5; 43,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 42,11</t>
+          <t>-6,53; 40,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 30,74</t>
+          <t>-9,75; 29,48</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 10,56</t>
+          <t>-3,87; 10,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,96</t>
+          <t>-1,17; 12,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 20,24</t>
+          <t>7,13; 20,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 16,59</t>
+          <t>-12,85; 16,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 30,3</t>
+          <t>-9,14; 30,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 49,29</t>
+          <t>-3,82; 52,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 109,87</t>
+          <t>28,94; 107,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 51,94</t>
+          <t>-32,55; 52,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 27,97</t>
+          <t>8,67; 27,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 19,33</t>
+          <t>0,26; 18,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 22,02</t>
+          <t>3,61; 22,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 8,53</t>
+          <t>-0,83; 8,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,68; 63,9</t>
+          <t>15,68; 60,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 83,38</t>
+          <t>0,33; 79,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 72,82</t>
+          <t>8,51; 73,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 120,5</t>
+          <t>-8,78; 109,03</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 15,29</t>
+          <t>-1,21; 15,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 11,25</t>
+          <t>-0,63; 11,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,78</t>
+          <t>-1,03; 15,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 9,27</t>
+          <t>-5,43; 9,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 46,82</t>
+          <t>-3,03; 45,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 94,4</t>
+          <t>-5,67; 103,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 51,74</t>
+          <t>-2,59; 51,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 25,97</t>
+          <t>-12,15; 26,14</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 7,18</t>
+          <t>-4,4; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 10,03</t>
+          <t>0,41; 9,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,35</t>
+          <t>0,59; 12,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 14,49</t>
+          <t>-13,86; 14,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 16,83</t>
+          <t>-9,36; 16,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 55,31</t>
+          <t>1,17; 52,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 33,89</t>
+          <t>1,42; 32,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 54,16</t>
+          <t>-46,32; 52,21</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 11,4</t>
+          <t>1,28; 11,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,7; 16,74</t>
+          <t>7,48; 16,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,15</t>
+          <t>5,49; 15,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 25,94</t>
+          <t>2,78; 27,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 26,56</t>
+          <t>2,63; 27,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,48; 75,63</t>
+          <t>27,79; 75,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,01; 42,02</t>
+          <t>13,53; 42,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,95; 236,73</t>
+          <t>8,33; 252,89</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,49</t>
+          <t>2,65; 7,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,55</t>
+          <t>6,21; 10,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,18</t>
+          <t>6,51; 11,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 14,16</t>
+          <t>0,84; 13,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,72</t>
+          <t>6,23; 18,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,35; 49,77</t>
+          <t>26,13; 50,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,7; 34,37</t>
+          <t>18,62; 35,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 54,42</t>
+          <t>3,31; 52,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P34A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 5,96</t>
+          <t>-10,83; 6,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 19,63</t>
+          <t>3,81; 19,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 16,38</t>
+          <t>1,16; 17,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 16,47</t>
+          <t>-1,79; 12,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 18,35</t>
+          <t>-27,18; 22,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 95,66</t>
+          <t>13,66; 93,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 60,35</t>
+          <t>2,01; 62,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 44,44</t>
+          <t>-3,53; 31,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>14,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 16,35</t>
+          <t>4,04; 16,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 19,91</t>
+          <t>7,87; 19,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 13,39</t>
+          <t>1,39; 13,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 21,57</t>
+          <t>7,59; 20,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 55,35</t>
+          <t>11,47; 55,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,79; 104,74</t>
+          <t>33,14; 103,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 50,27</t>
+          <t>3,81; 50,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 65,82</t>
+          <t>17,45; 57,54</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 6,45</t>
+          <t>-9,07; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 6,95</t>
+          <t>-5,77; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,54</t>
+          <t>-2,38; 12,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 9,54</t>
+          <t>-4,0; 9,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 16,82</t>
+          <t>-19,97; 16,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 43,6</t>
+          <t>-26,47; 43,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 40,49</t>
+          <t>-6,65; 43,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 29,48</t>
+          <t>-9,8; 30,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 10,45</t>
+          <t>-3,51; 11,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 12,7</t>
+          <t>-1,39; 12,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 20,17</t>
+          <t>6,65; 19,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 16,61</t>
+          <t>-3,17; 12,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 30,96</t>
+          <t>-8,45; 32,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 52,95</t>
+          <t>-4,72; 51,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 107,91</t>
+          <t>26,27; 106,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 52,95</t>
+          <t>-7,72; 44,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 27,04</t>
+          <t>7,72; 29,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 18,7</t>
+          <t>0,82; 18,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 22,51</t>
+          <t>3,88; 22,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,11</t>
+          <t>-0,03; 9,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 60,29</t>
+          <t>15,22; 66,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 79,68</t>
+          <t>2,9; 81,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 73,19</t>
+          <t>10,57; 80,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 109,03</t>
+          <t>-2,16; 133,27</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,13</t>
+          <t>-1,24; 15,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,6</t>
+          <t>-1,55; 11,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 15,35</t>
+          <t>-0,76; 15,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 9,29</t>
+          <t>-7,07; 7,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 45,9</t>
+          <t>-3,04; 48,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 103,5</t>
+          <t>-11,15; 96,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 51,77</t>
+          <t>-2,1; 52,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 26,14</t>
+          <t>-15,52; 20,32</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,92</t>
+          <t>-3,93; 7,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 9,53</t>
+          <t>0,42; 10,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 12,04</t>
+          <t>1,34; 12,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 14,19</t>
+          <t>6,56; 16,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 16,42</t>
+          <t>-8,24; 17,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 52,45</t>
+          <t>1,21; 55,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 32,59</t>
+          <t>3,1; 33,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 52,21</t>
+          <t>20,22; 65,24</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,72</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,43</t>
+          <t>0,69; 11,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 16,74</t>
+          <t>7,42; 16,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 15,12</t>
+          <t>5,07; 15,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 27,19</t>
+          <t>0,59; 9,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 27,08</t>
+          <t>0,89; 25,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,79; 75,5</t>
+          <t>26,81; 74,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,53; 42,54</t>
+          <t>12,98; 42,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 252,89</t>
+          <t>1,57; 34,08</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,45</t>
+          <t>2,44; 7,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,68</t>
+          <t>6,25; 10,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,37</t>
+          <t>6,48; 11,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,63</t>
+          <t>4,98; 9,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,6</t>
+          <t>5,71; 18,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,13; 50,2</t>
+          <t>26,67; 49,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,62; 35,42</t>
+          <t>18,58; 34,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,31; 52,15</t>
+          <t>14,15; 29,71</t>
         </is>
       </c>
     </row>
